--- a/data/raw/김포 25년/항공통계상세조회(노선) (5).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (5).xlsx
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>10615</t>
-  </si>
-  <si>
-    <t>1898204</t>
-  </si>
-  <si>
-    <t>15745</t>
+    <t>5319</t>
+  </si>
+  <si>
+    <t>954374</t>
+  </si>
+  <si>
+    <t>7824</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,172 +53,172 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
-    <t>434</t>
-  </si>
-  <si>
-    <t>79978</t>
-  </si>
-  <si>
-    <t>915</t>
+    <t>217</t>
+  </si>
+  <si>
+    <t>39801</t>
+  </si>
+  <si>
+    <t>483</t>
   </si>
   <si>
     <t>광주(KWJ)</t>
   </si>
   <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>7038</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>88487</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>나고야(NGO)</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>5105</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>5026</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>83937</t>
+  </si>
+  <si>
+    <t>1725</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>12800</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>7134</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>9954</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>9214</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>10410</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>3443</t>
+  </si>
+  <si>
+    <t>641068</t>
+  </si>
+  <si>
+    <t>4359</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>6241</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>1744</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>홍차오(SHA)</t>
+  </si>
+  <si>
     <t>124</t>
   </si>
   <si>
-    <t>14425</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1144</t>
-  </si>
-  <si>
-    <t>175426</t>
-  </si>
-  <si>
-    <t>709</t>
-  </si>
-  <si>
-    <t>나고야(NGO)</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>10373</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>9994</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>742</t>
-  </si>
-  <si>
-    <t>164499</t>
-  </si>
-  <si>
-    <t>2645</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>25122</t>
-  </si>
-  <si>
-    <t>274</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>120</t>
-  </si>
-  <si>
-    <t>14350</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
-  </si>
-  <si>
-    <t>20107</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>173</t>
-  </si>
-  <si>
-    <t>18679</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>182</t>
-  </si>
-  <si>
-    <t>21255</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>6873</t>
-  </si>
-  <si>
-    <t>1275934</t>
-  </si>
-  <si>
-    <t>9413</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>12480</t>
-  </si>
-  <si>
-    <t>141</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>3459</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>248</t>
-  </si>
-  <si>
-    <t>52123</t>
-  </si>
-  <si>
-    <t>975</t>
+    <t>26415</t>
+  </si>
+  <si>
+    <t>313</t>
   </si>
 </sst>
 </file>
@@ -409,7 +409,7 @@
         <v>29</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -420,16 +420,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -440,16 +440,16 @@
         <v>11</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -460,16 +460,16 @@
         <v>11</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -480,16 +480,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s" s="0">
         <v>17</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -500,16 +500,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -520,16 +520,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -540,16 +540,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -560,16 +560,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -580,10 +580,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s" s="0">
         <v>63</v>
